--- a/Employee_Reports_wi52/Elesor JR Cas Frondozo Q0430.xlsx
+++ b/Employee_Reports_wi52/Elesor JR Cas Frondozo Q0430.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
